--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2020_T2_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2020_T2_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>78</t>
+    <t>72</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.811</t>
-  </si>
-  <si>
-    <t>(0.098)</t>
-  </si>
-  <si>
-    <t>4.885</t>
-  </si>
-  <si>
-    <t>(0.543)</t>
-  </si>
-  <si>
-    <t>1.328</t>
-  </si>
-  <si>
-    <t>(0.381)</t>
-  </si>
-  <si>
-    <t>12.580</t>
-  </si>
-  <si>
-    <t>(4.442)</t>
-  </si>
-  <si>
-    <t>0.916</t>
-  </si>
-  <si>
-    <t>(0.166)</t>
-  </si>
-  <si>
-    <t>5.423</t>
-  </si>
-  <si>
-    <t>(0.714)</t>
-  </si>
-  <si>
-    <t>9.168</t>
-  </si>
-  <si>
-    <t>(4.477)</t>
-  </si>
-  <si>
-    <t>0.357</t>
-  </si>
-  <si>
-    <t>(0.053)</t>
-  </si>
-  <si>
-    <t>10.093</t>
-  </si>
-  <si>
-    <t>(1.965)</t>
-  </si>
-  <si>
-    <t>14.060</t>
-  </si>
-  <si>
-    <t>(7.542)</t>
+    <t>0.849</t>
+  </si>
+  <si>
+    <t>(0.101)</t>
+  </si>
+  <si>
+    <t>5.236</t>
+  </si>
+  <si>
+    <t>(0.566)</t>
+  </si>
+  <si>
+    <t>1.439</t>
+  </si>
+  <si>
+    <t>(0.410)</t>
+  </si>
+  <si>
+    <t>5.831</t>
+  </si>
+  <si>
+    <t>(0.957)</t>
+  </si>
+  <si>
+    <t>0.795</t>
+  </si>
+  <si>
+    <t>(0.081)</t>
+  </si>
+  <si>
+    <t>5.806</t>
+  </si>
+  <si>
+    <t>(0.755)</t>
+  </si>
+  <si>
+    <t>2.361</t>
+  </si>
+  <si>
+    <t>(0.843)</t>
+  </si>
+  <si>
+    <t>0.387</t>
+  </si>
+  <si>
+    <t>(0.056)</t>
+  </si>
+  <si>
+    <t>7.025</t>
+  </si>
+  <si>
+    <t>(1.213)</t>
+  </si>
+  <si>
+    <t>4.683</t>
+  </si>
+  <si>
+    <t>(0.735)</t>
   </si>
   <si>
     <t>38</t>
@@ -198,7 +198,7 @@
     <t>(0.589)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-0.121</t>
-  </si>
-  <si>
-    <t>-0.464</t>
-  </si>
-  <si>
-    <t>0.854</t>
-  </si>
-  <si>
-    <t>-7.224</t>
-  </si>
-  <si>
-    <t>-0.179</t>
-  </si>
-  <si>
-    <t>0.366</t>
-  </si>
-  <si>
-    <t>-7.759</t>
-  </si>
-  <si>
-    <t>-0.018</t>
-  </si>
-  <si>
-    <t>-3.659</t>
-  </si>
-  <si>
-    <t>-9.625</t>
+    <t>-0.159</t>
+  </si>
+  <si>
+    <t>-0.815</t>
+  </si>
+  <si>
+    <t>0.743</t>
+  </si>
+  <si>
+    <t>-0.474</t>
+  </si>
+  <si>
+    <t>-0.058</t>
+  </si>
+  <si>
+    <t>-0.016</t>
+  </si>
+  <si>
+    <t>-0.952</t>
+  </si>
+  <si>
+    <t>-0.047</t>
+  </si>
+  <si>
+    <t>-0.591</t>
+  </si>
+  <si>
+    <t>-0.249</t>
   </si>
 </sst>
 </file>
